--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5x3</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5x3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-27.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1938,19 +1938,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2418,19 +2418,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S25" t="n">
